--- a/reports/inventory_report_20260705_1800.xlsx
+++ b/reports/inventory_report_20260705_1800.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/inventory_report_20260705_1800.xlsx
+++ b/reports/inventory_report_20260705_1800.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/reports/inventory_report_20260705_1800.xlsx
+++ b/reports/inventory_report_20260705_1800.xlsx
@@ -413,34 +413,55 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Stock Level Summary Report</t>
+          <t>&lt;!DOCTYPE HTML PUBLIC "-//IETF//DTD HTML 2.0//EN"&gt;</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B0961005</t>
+          <t>&lt;html&gt;&lt;head&gt;</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hong Kong online Community pharmacy superstore</t>
+          <t>&lt;title&gt;404 Not Found&lt;/title&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026/07/05</t>
+          <t>&lt;/head&gt;&lt;body&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>&lt;h1&gt;Not Found&lt;/h1&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The requested URL /merchant_reports/stocklevel_report/B0961005/stocklevel_B0961005_20260705.csv was not found on this server.&lt;/p&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>&lt;/body&gt;&lt;/html&gt;</t>
         </is>
       </c>
     </row>
